--- a/VALIDA.xlsx
+++ b/VALIDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beca\OneDrive\Escritorio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAFC81E-584B-42DC-B8C9-17E6831C21A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C607981-C679-46AC-B3BB-DA7A3AE498FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -112,6 +112,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -392,13 +393,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -406,7 +407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>46072</v>
       </c>
@@ -414,7 +415,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>46077</v>
       </c>
@@ -422,7 +423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>46087</v>
       </c>
@@ -430,9 +431,21 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>46092</v>
+      </c>
+      <c r="B5" s="5">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>46101</v>
+      </c>
+      <c r="B6">
+        <v>1340</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
